--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR_Mean.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR_Mean.xlsx
@@ -381,65 +381,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
+          <t>CAMA-1</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.5428313482417512</v>
+        <v>0.8009852602328971</v>
       </c>
       <c r="C2">
-        <v>0.6280907503334283</v>
+        <v>0.549806292188348</v>
       </c>
       <c r="D2">
-        <v>0.8268952893398462</v>
+        <v>1.092192857142857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.7872008398489432</v>
+        <v>0.8104027136981351</v>
       </c>
       <c r="C3">
-        <v>0.8964126105951561</v>
+        <v>0.6545053357513249</v>
       </c>
       <c r="D3">
-        <v>0.6283277530969766</v>
+        <v>0.4546576376802317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
+          <t>MCF-7</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.8009852602328971</v>
+        <v>0.5428313482417512</v>
       </c>
       <c r="C4">
-        <v>0.549806292188348</v>
+        <v>0.6280907503334283</v>
       </c>
       <c r="D4">
-        <v>1.092192857142857</v>
+        <v>0.8268952893398462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.8104027136981351</v>
+        <v>0.7872008398489432</v>
       </c>
       <c r="C5">
-        <v>0.6545053357513249</v>
+        <v>0.8964126105951561</v>
       </c>
       <c r="D5">
-        <v>0.4546576376802317</v>
+        <v>0.6283277530969766</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
+          <t>CAMA-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
+          <t>MCF-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
